--- a/src/src/main/webapp/portal/zkb/orderHistory/Order_History_Service_Template_EN.xlsx
+++ b/src/src/main/webapp/portal/zkb/orderHistory/Order_History_Service_Template_EN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (4)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (12)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{330E4121-4809-4CB4-9DC9-4E417082B3BD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E0DB67-DB3F-44C8-ADD2-93BBC2F801FD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,9 +28,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
-    <t>FW</t>
-  </si>
-  <si>
     <t>RSESup</t>
   </si>
   <si>
@@ -40,25 +37,49 @@
     <t>Act</t>
   </si>
   <si>
+    <t>归还</t>
+  </si>
+  <si>
     <t>Comments</t>
   </si>
   <si>
-    <t>Call No</t>
-  </si>
-  <si>
     <t>Srowner</t>
   </si>
   <si>
-    <t>Srclose</t>
-  </si>
-  <si>
-    <t>IBowner</t>
-  </si>
-  <si>
-    <t>IBZone</t>
-  </si>
-  <si>
-    <t>Source</t>
+    <t>删除</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>人工名额</t>
+  </si>
+  <si>
+    <t>备件名额</t>
+  </si>
+  <si>
+    <t>探头名额</t>
+  </si>
+  <si>
+    <t>人工，备件，保养联合名额</t>
+  </si>
+  <si>
+    <t>类别</t>
+  </si>
+  <si>
+    <t>探头类型</t>
+  </si>
+  <si>
+    <t>是否使用名额Y/N</t>
+  </si>
+  <si>
+    <t>CallNo</t>
+  </si>
+  <si>
+    <t>owner name</t>
+  </si>
+  <si>
+    <t>SR Status</t>
   </si>
   <si>
     <t>System Id</t>
@@ -67,9 +88,6 @@
     <t>Data Type</t>
   </si>
   <si>
-    <t>Region</t>
-  </si>
-  <si>
     <t>Agent</t>
   </si>
   <si>
@@ -88,15 +106,9 @@
     <t>IB Quantity</t>
   </si>
   <si>
-    <t>Spare Parts Quantity</t>
-  </si>
-  <si>
     <t>Event Date</t>
   </si>
   <si>
-    <t>Event Quarter</t>
-  </si>
-  <si>
     <t>System No</t>
   </si>
   <si>
@@ -124,25 +136,13 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>Spare Parts Left</t>
-  </si>
-  <si>
-    <t>Spare Parts Return</t>
-  </si>
-  <si>
     <t>Insurance Description</t>
   </si>
   <si>
-    <t>Arrangement</t>
-  </si>
-  <si>
-    <t>Delete</t>
-  </si>
-  <si>
-    <t>Data Type can not be null</t>
-  </si>
-  <si>
-    <t>update data when filed of system id is not null</t>
+    <t>System id can not be null</t>
+  </si>
+  <si>
+    <t>update when id not be null</t>
   </si>
 </sst>
 </file>
@@ -494,177 +494,178 @@
     <col min="6" max="6" width="26.77734375" style="2" customWidth="1"/>
     <col min="7" max="7" width="26.6640625" style="4" customWidth="1"/>
     <col min="8" max="8" width="22.77734375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="20.44140625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="23.33203125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="19.77734375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="20.33203125" style="4" customWidth="1"/>
-    <col min="13" max="13" width="26.88671875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="24.33203125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="20.21875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="23.5546875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="19.88671875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="16.77734375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="18.88671875" style="5" customWidth="1"/>
-    <col min="20" max="20" width="20.6640625" style="2" customWidth="1"/>
-    <col min="21" max="21" width="17.88671875" style="2" customWidth="1"/>
-    <col min="22" max="22" width="25.88671875" style="3" customWidth="1"/>
-    <col min="23" max="24" width="19.6640625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="23.21875" style="3" customWidth="1"/>
-    <col min="26" max="26" width="17.88671875" style="2" customWidth="1"/>
-    <col min="27" max="27" width="21.44140625" style="2" customWidth="1"/>
-    <col min="28" max="28" width="21.88671875" style="2" customWidth="1"/>
-    <col min="29" max="29" width="19.33203125" style="2" customWidth="1"/>
-    <col min="30" max="30" width="21.6640625" style="2" customWidth="1"/>
-    <col min="31" max="31" width="18.88671875" style="2" customWidth="1"/>
-    <col min="32" max="32" width="19.6640625" style="2" customWidth="1"/>
-    <col min="33" max="33" width="18.5546875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="17.44140625" style="2" customWidth="1"/>
-    <col min="35" max="35" width="22.109375" style="2" customWidth="1"/>
-    <col min="36" max="36" width="17.33203125" style="2" customWidth="1"/>
+    <col min="9" max="12" width="20.44140625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="26.6640625" style="3" customWidth="1"/>
+    <col min="14" max="15" width="20.33203125" style="4" customWidth="1"/>
+    <col min="16" max="16" width="24.33203125" style="2" customWidth="1"/>
+    <col min="17" max="17" width="20.21875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="23.5546875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="19.88671875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="16.77734375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="18.88671875" style="5" customWidth="1"/>
+    <col min="22" max="23" width="17.33203125" style="2" customWidth="1"/>
+    <col min="24" max="24" width="17.88671875" style="2" customWidth="1"/>
+    <col min="25" max="25" width="25.88671875" style="3" customWidth="1"/>
+    <col min="26" max="27" width="19.6640625" style="2" customWidth="1"/>
+    <col min="28" max="28" width="17.88671875" style="2" customWidth="1"/>
+    <col min="29" max="29" width="21.44140625" style="2" customWidth="1"/>
+    <col min="30" max="33" width="22.109375" style="2" customWidth="1"/>
+    <col min="34" max="36" width="21.6640625" style="2" customWidth="1"/>
     <col min="37" max="37" width="24.5546875" style="2" customWidth="1"/>
     <col min="38" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576 Y2:Y1048576" xr:uid="{75CC79BC-1A63-40FD-BC38-55F9C3D85FDE}">
+  <dataValidations count="11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{2328E975-6B95-406D-A1DC-1FE2591DFBCB}">
+      <formula1>"DI、PCB,US、Biomed,LCS,US探头"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2:AK1048576 AF2:AF1048576" xr:uid="{A51DFEA4-85BF-4073-84EF-6568AF66F0A5}">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:H1048576 N2:N1048576" xr:uid="{BF8FCE24-812C-4E76-8679-0BCA72EC8232}">
+      <formula1>1</formula1>
+      <formula2>72686</formula2>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:M1048576" xr:uid="{ABCE1C6A-DD95-44E2-ADD1-D66EF47B9D56}">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576" xr:uid="{F1A10A8C-0601-4CEA-83CB-2DF02510BAA1}">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{2328E975-6B95-406D-A1DC-1FE2591DFBCB}">
-      <formula1>"DI、PCB,US、Biomed,LCS,US探头"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2:AK1048576" xr:uid="{A51DFEA4-85BF-4073-84EF-6568AF66F0A5}">
-      <formula1>"Y,N"</formula1>
-    </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576 H2:H1048576 L2:L1048576" xr:uid="{BF8FCE24-812C-4E76-8679-0BCA72EC8232}">
-      <formula1>1</formula1>
-      <formula2>72686</formula2>
-    </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576" xr:uid="{ABCE1C6A-DD95-44E2-ADD1-D66EF47B9D56}">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576" xr:uid="{F1A10A8C-0601-4CEA-83CB-2DF02510BAA1}">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576" xr:uid="{DD333222-F32B-486C-95EA-C7A2B140EC69}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576" xr:uid="{DD333222-F32B-486C-95EA-C7A2B140EC69}">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576" xr:uid="{CDDC3228-3434-4A33-AC68-845488680DFF}">
+      <formula1>"探头订单,备件订单,人工订单,工具订单"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576" xr:uid="{D311B7E8-EBC8-42E3-BDCA-16C6F9AAA5F8}">
+      <formula1>"N/A,cancel,badreturn,goodreturn,DOA,shortlife"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE1048576" xr:uid="{55F8E1A3-69FF-42C0-9015-A55922B573DE}">
+      <formula1>"N/A,普通,特殊,高值"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH1048576" xr:uid="{11549471-4591-4EDB-ABC9-AB8AD11D3728}">
+      <formula1>"代理商,GE FE,Vendor2.0 FE,MVS FE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576" xr:uid="{F5FF3C40-8578-4D7C-9E18-44D08239F03A}">
+      <formula1>"N/A,新入保,已入保"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -678,7 +679,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
-    <col min="2" max="2" width="74.109375" customWidth="1"/>
+    <col min="2" max="2" width="35.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
